--- a/Código/Controles/15. Eliminación de primeros ítems (Generales).xlsx
+++ b/Código/Controles/15. Eliminación de primeros ítems (Generales).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:NL51"/>
+  <dimension ref="A1:MZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,130 +2181,70 @@
       </c>
       <c r="MM1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro</t>
+          <t>Sentimiento_Fase_Final</t>
         </is>
       </c>
       <c r="MN1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro</t>
+          <t>Evento_Estresante</t>
         </is>
       </c>
       <c r="MO1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con</t>
+          <t>Sabia_Del_Experimento</t>
         </is>
       </c>
       <c r="MP1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con</t>
+          <t>Usa_Sustancias</t>
         </is>
       </c>
       <c r="MQ1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro_Izq</t>
+          <t>Tabaco</t>
         </is>
       </c>
       <c r="MR1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro_Izq</t>
+          <t>Alcohol</t>
         </is>
       </c>
       <c r="MS1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Pro_Der</t>
+          <t>Marihuana</t>
         </is>
       </c>
       <c r="MT1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Pro_Der</t>
+          <t>Drogas_Recreativas</t>
         </is>
       </c>
       <c r="MU1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con_Izq</t>
+          <t>Cual_Droga_Recreativa</t>
         </is>
       </c>
       <c r="MV1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con_Izq</t>
+          <t>Medicamentos</t>
         </is>
       </c>
       <c r="MW1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Opinion_Con_Der</t>
+          <t>Cual_Medicamento</t>
         </is>
       </c>
       <c r="MX1" s="1" t="inlineStr">
         <is>
-          <t>Cambio_Tiempo_Con_Der</t>
+          <t>Otras_Sustancias</t>
         </is>
       </c>
       <c r="MY1" s="1" t="inlineStr">
         <is>
-          <t>Sentimiento_Fase_Final</t>
+          <t>Horas_Sueno_Promedio</t>
         </is>
       </c>
       <c r="MZ1" s="1" t="inlineStr">
-        <is>
-          <t>Evento_Estresante</t>
-        </is>
-      </c>
-      <c r="NA1" s="1" t="inlineStr">
-        <is>
-          <t>Sabia_Del_Experimento</t>
-        </is>
-      </c>
-      <c r="NB1" s="1" t="inlineStr">
-        <is>
-          <t>Usa_Sustancias</t>
-        </is>
-      </c>
-      <c r="NC1" s="1" t="inlineStr">
-        <is>
-          <t>Tabaco</t>
-        </is>
-      </c>
-      <c r="ND1" s="1" t="inlineStr">
-        <is>
-          <t>Alcohol</t>
-        </is>
-      </c>
-      <c r="NE1" s="1" t="inlineStr">
-        <is>
-          <t>Marihuana</t>
-        </is>
-      </c>
-      <c r="NF1" s="1" t="inlineStr">
-        <is>
-          <t>Drogas_Recreativas</t>
-        </is>
-      </c>
-      <c r="NG1" s="1" t="inlineStr">
-        <is>
-          <t>Cual_Droga_Recreativa</t>
-        </is>
-      </c>
-      <c r="NH1" s="1" t="inlineStr">
-        <is>
-          <t>Medicamentos</t>
-        </is>
-      </c>
-      <c r="NI1" s="1" t="inlineStr">
-        <is>
-          <t>Cual_Medicamento</t>
-        </is>
-      </c>
-      <c r="NJ1" s="1" t="inlineStr">
-        <is>
-          <t>Otras_Sustancias</t>
-        </is>
-      </c>
-      <c r="NK1" s="1" t="inlineStr">
-        <is>
-          <t>Horas_Sueno_Promedio</t>
-        </is>
-      </c>
-      <c r="NL1" s="1" t="inlineStr">
         <is>
           <t>Sueno_Noche_Anterior</t>
         </is>
@@ -3317,108 +3257,72 @@
       <c r="ML2" t="n">
         <v>6.010166666666666</v>
       </c>
-      <c r="MM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX2" t="n">
-        <v>0</v>
+      <c r="MM2" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR2" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU2" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV2" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW2" t="inlineStr">
+        <is>
+          <t>levo, disatval, tamoxifeno...y 4 pastillas mas</t>
+        </is>
+      </c>
+      <c r="MX2" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY2" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND2" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG2" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH2" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI2" t="inlineStr">
-        <is>
-          <t>levo, disatval, tamoxifeno...y 4 pastillas mas</t>
-        </is>
-      </c>
-      <c r="NJ2" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK2" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL2" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -4431,108 +4335,72 @@
       <c r="ML3" t="n">
         <v>6.608428571428572</v>
       </c>
-      <c r="MM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX3" t="n">
-        <v>0</v>
+      <c r="MM3" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR3" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU3" t="inlineStr">
+        <is>
+          <t>vino</t>
+        </is>
+      </c>
+      <c r="MV3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX3" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY3" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND3" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG3" t="inlineStr">
-        <is>
-          <t>vino</t>
-        </is>
-      </c>
-      <c r="NH3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ3" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK3" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL3" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -5545,108 +5413,72 @@
       <c r="ML4" t="n">
         <v>11.23333333333333</v>
       </c>
-      <c r="MM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX4" t="n">
-        <v>0</v>
+      <c r="MM4" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU4" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV4" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">losartan </t>
+        </is>
+      </c>
+      <c r="MX4" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY4" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG4" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH4" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">losartan </t>
-        </is>
-      </c>
-      <c r="NJ4" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK4" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL4" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -6659,108 +6491,72 @@
       <c r="ML5" t="n">
         <v>6.406999999999999</v>
       </c>
-      <c r="MM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX5" t="n">
-        <v>0</v>
+      <c r="MM5" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR5" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT5" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU5" t="inlineStr">
+        <is>
+          <t>vino</t>
+        </is>
+      </c>
+      <c r="MV5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW5" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX5" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY5" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ5" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND5" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF5" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG5" t="inlineStr">
-        <is>
-          <t>vino</t>
-        </is>
-      </c>
-      <c r="NH5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI5" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ5" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK5" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL5" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -7773,104 +7569,68 @@
       <c r="ML6" t="n">
         <v>6.204499999999999</v>
       </c>
-      <c r="MM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX6" t="n">
-        <v>0</v>
+      <c r="MM6" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR6" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aperitivo </t>
+        </is>
+      </c>
+      <c r="MV6" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MW6" t="inlineStr"/>
+      <c r="MX6" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY6" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND6" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF6" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aperitivo </t>
-        </is>
-      </c>
-      <c r="NH6" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NI6" t="inlineStr"/>
-      <c r="NJ6" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK6" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL6" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -8883,108 +8643,72 @@
       <c r="ML7" t="n">
         <v>11.997875</v>
       </c>
-      <c r="MM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX7" t="n">
-        <v>0</v>
+      <c r="MM7" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP7" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ7" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR7" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU7" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW7" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX7" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY7" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB7" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC7" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND7" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG7" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI7" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ7" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK7" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL7" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -9997,108 +9721,72 @@
       <c r="ML8" t="n">
         <v>8.716125</v>
       </c>
-      <c r="MM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX8" t="n">
-        <v>0</v>
+      <c r="MM8" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP8" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ8" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU8" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW8" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX8" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY8" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB8" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC8" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG8" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI8" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ8" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK8" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL8" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -11111,108 +10799,72 @@
       <c r="ML9" t="n">
         <v>10.85516666666667</v>
       </c>
-      <c r="MM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX9" t="n">
-        <v>0</v>
+      <c r="MM9" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN9" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR9" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU9" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV9" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pastillas anticonceptivas, minoxidil oral, </t>
+        </is>
+      </c>
+      <c r="MX9" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY9" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ9" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND9" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG9" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH9" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pastillas anticonceptivas, minoxidil oral, </t>
-        </is>
-      </c>
-      <c r="NJ9" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK9" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL9" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -12225,108 +11877,72 @@
       <c r="ML10" t="n">
         <v>5.6165</v>
       </c>
-      <c r="MM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX10" t="n">
-        <v>0</v>
+      <c r="MM10" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR10" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU10" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW10" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX10" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY10" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ10" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND10" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG10" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI10" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ10" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK10" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL10" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -13339,108 +12955,72 @@
       <c r="ML11" t="n">
         <v>9.996166666666667</v>
       </c>
-      <c r="MM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX11" t="n">
-        <v>0</v>
+      <c r="MM11" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR11" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU11" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW11" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX11" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY11" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND11" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG11" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI11" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ11" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK11" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL11" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -14453,108 +14033,72 @@
       <c r="ML12" t="n">
         <v>5.83</v>
       </c>
-      <c r="MM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX12" t="n">
-        <v>0</v>
+      <c r="MM12" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN12" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR12" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU12" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW12" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX12" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY12" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ12" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND12" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG12" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI12" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ12" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK12" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL12" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -15567,108 +15111,72 @@
       <c r="ML13" t="n">
         <v>16.13495</v>
       </c>
-      <c r="MM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX13" t="n">
-        <v>0</v>
+      <c r="MM13" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU13" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW13" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX13" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY13" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG13" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI13" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ13" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK13" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL13" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -16681,108 +16189,72 @@
       <c r="ML14" t="n">
         <v>9.454000000000001</v>
       </c>
-      <c r="MM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX14" t="n">
-        <v>0</v>
+      <c r="MM14" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR14" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU14" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW14" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX14" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY14" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND14" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG14" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI14" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ14" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK14" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL14" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -17795,108 +17267,72 @@
       <c r="ML15" t="n">
         <v>10.98875</v>
       </c>
-      <c r="MM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX15" t="n">
-        <v>0</v>
+      <c r="MM15" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP15" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ15" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR15" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS15" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU15" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV15" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW15" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX15" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY15" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB15" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC15" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND15" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE15" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG15" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH15" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI15" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ15" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK15" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL15" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -18909,108 +18345,72 @@
       <c r="ML16" t="n">
         <v>10.105</v>
       </c>
-      <c r="MM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX16" t="n">
-        <v>0</v>
+      <c r="MM16" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR16" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU16" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV16" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW16" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX16" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
       </c>
       <c r="MY16" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND16" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG16" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH16" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI16" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ16" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NK16" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL16" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -20023,108 +19423,72 @@
       <c r="ML17" t="n">
         <v>5.693214285714286</v>
       </c>
-      <c r="MM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX17" t="n">
-        <v>0</v>
+      <c r="MM17" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR17" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS17" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU17" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW17" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX17" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY17" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND17" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE17" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG17" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI17" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ17" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK17" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL17" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -21137,108 +20501,72 @@
       <c r="ML18" t="n">
         <v>7.350000000000001</v>
       </c>
-      <c r="MM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX18" t="n">
-        <v>0</v>
+      <c r="MM18" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP18" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ18" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR18" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS18" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MT18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU18" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW18" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX18" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY18" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB18" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC18" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND18" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE18" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NF18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG18" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI18" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ18" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK18" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL18" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -22251,108 +21579,72 @@
       <c r="ML19" t="n">
         <v>9.3894</v>
       </c>
-      <c r="MM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX19" t="n">
-        <v>0</v>
+      <c r="MM19" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP19" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ19" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR19" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS19" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU19" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV19" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW19" t="inlineStr">
+        <is>
+          <t>aco- fluoxetina</t>
+        </is>
+      </c>
+      <c r="MX19" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
       </c>
       <c r="MY19" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB19" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC19" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND19" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE19" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG19" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH19" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI19" t="inlineStr">
-        <is>
-          <t>aco- fluoxetina</t>
-        </is>
-      </c>
-      <c r="NJ19" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NK19" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL19" t="inlineStr">
         <is>
           <t>mas de 8 horas</t>
         </is>
@@ -23365,108 +22657,72 @@
       <c r="ML20" t="n">
         <v>7.11225</v>
       </c>
-      <c r="MM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX20" t="n">
-        <v>0</v>
+      <c r="MM20" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP20" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ20" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR20" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS20" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MT20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marihuana </t>
+        </is>
+      </c>
+      <c r="MV20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW20" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX20" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY20" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ20" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB20" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC20" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND20" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE20" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NF20" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marihuana </t>
-        </is>
-      </c>
-      <c r="NH20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI20" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ20" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK20" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL20" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -24479,108 +23735,72 @@
       <c r="ML21" t="n">
         <v>6.40375</v>
       </c>
-      <c r="MM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX21" t="n">
-        <v>0</v>
+      <c r="MM21" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU21" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW21" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX21" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY21" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG21" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI21" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ21" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK21" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL21" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -25593,108 +24813,72 @@
       <c r="ML22" t="n">
         <v>6.193300000000001</v>
       </c>
-      <c r="MM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX22" t="n">
-        <v>0</v>
+      <c r="MM22" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR22" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU22" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW22" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX22" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY22" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND22" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG22" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI22" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ22" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK22" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL22" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -26707,104 +25891,68 @@
       <c r="ML23" t="n">
         <v>3.772166666666667</v>
       </c>
-      <c r="MM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX23" t="n">
-        <v>0</v>
+      <c r="MM23" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP23" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ23" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR23" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS23" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU23" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV23" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MW23" t="inlineStr"/>
+      <c r="MX23" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY23" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB23" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC23" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND23" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE23" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG23" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH23" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NI23" t="inlineStr"/>
-      <c r="NJ23" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK23" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL23" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -27817,108 +26965,72 @@
       <c r="ML24" t="n">
         <v>10.45833333333333</v>
       </c>
-      <c r="MM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX24" t="n">
-        <v>0</v>
+      <c r="MM24" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN24" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU24" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW24" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX24" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY24" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ24" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG24" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI24" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ24" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK24" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL24" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -28931,108 +28043,72 @@
       <c r="ML25" t="n">
         <v>23.63566666666667</v>
       </c>
-      <c r="MM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX25" t="n">
-        <v>0</v>
+      <c r="MM25" t="inlineStr">
+        <is>
+          <t>nervioso</t>
+        </is>
+      </c>
+      <c r="MN25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP25" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ25" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR25" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU25" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV25" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MW25" t="inlineStr">
+        <is>
+          <t>paracetamol</t>
+        </is>
+      </c>
+      <c r="MX25" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY25" t="inlineStr">
         <is>
-          <t>nervioso</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB25" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC25" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND25" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG25" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH25" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NI25" t="inlineStr">
-        <is>
-          <t>paracetamol</t>
-        </is>
-      </c>
-      <c r="NJ25" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK25" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL25" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -30045,108 +29121,72 @@
       <c r="ML26" t="n">
         <v>9.263375</v>
       </c>
-      <c r="MM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX26" t="n">
-        <v>0</v>
+      <c r="MM26" t="inlineStr">
+        <is>
+          <t>nervioso</t>
+        </is>
+      </c>
+      <c r="MN26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU26" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW26" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX26" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY26" t="inlineStr">
         <is>
-          <t>nervioso</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG26" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI26" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ26" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK26" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL26" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -31159,108 +30199,72 @@
       <c r="ML27" t="n">
         <v>9.3255</v>
       </c>
-      <c r="MM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX27" t="n">
-        <v>0</v>
+      <c r="MM27" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN27" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR27" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS27" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MT27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU27" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV27" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW27" t="inlineStr">
+        <is>
+          <t>clonazepan y sertralina</t>
+        </is>
+      </c>
+      <c r="MX27" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY27" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ27" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND27" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE27" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NF27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG27" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH27" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI27" t="inlineStr">
-        <is>
-          <t>clonazepan y sertralina</t>
-        </is>
-      </c>
-      <c r="NJ27" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK27" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL27" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -32273,108 +31277,72 @@
       <c r="ML28" t="n">
         <v>10.9963</v>
       </c>
-      <c r="MM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX28" t="n">
-        <v>0</v>
+      <c r="MM28" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP28" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MQ28" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MR28" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS28" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU28" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV28" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW28" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX28" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY28" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB28" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NC28" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ND28" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE28" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG28" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH28" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI28" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ28" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK28" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL28" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -33387,108 +32355,72 @@
       <c r="ML29" t="n">
         <v>12.19717857142857</v>
       </c>
-      <c r="MM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX29" t="n">
-        <v>0</v>
+      <c r="MM29" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR29" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU29" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV29" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW29" t="inlineStr">
+        <is>
+          <t>tryptanol para migraña</t>
+        </is>
+      </c>
+      <c r="MX29" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY29" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND29" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG29" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH29" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI29" t="inlineStr">
-        <is>
-          <t>tryptanol para migraña</t>
-        </is>
-      </c>
-      <c r="NJ29" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK29" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL29" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -34501,108 +33433,72 @@
       <c r="ML30" t="n">
         <v>8.1622</v>
       </c>
-      <c r="MM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX30" t="n">
-        <v>0</v>
+      <c r="MM30" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR30" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU30" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW30" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX30" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY30" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND30" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG30" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI30" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ30" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK30" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL30" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -35615,108 +34511,72 @@
       <c r="ML31" t="n">
         <v>11.749375</v>
       </c>
-      <c r="MM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX31" t="n">
-        <v>0</v>
+      <c r="MM31" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP31" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MQ31" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MR31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU31" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV31" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW31" t="inlineStr">
+        <is>
+          <t>levotiroxina exitalopram</t>
+        </is>
+      </c>
+      <c r="MX31" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY31" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB31" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NC31" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="ND31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG31" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH31" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI31" t="inlineStr">
-        <is>
-          <t>levotiroxina exitalopram</t>
-        </is>
-      </c>
-      <c r="NJ31" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK31" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL31" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -36729,108 +35589,72 @@
       <c r="ML32" t="n">
         <v>7.234399999999999</v>
       </c>
-      <c r="MM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX32" t="n">
-        <v>0</v>
+      <c r="MM32" t="inlineStr">
+        <is>
+          <t>nervioso</t>
+        </is>
+      </c>
+      <c r="MN32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU32" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW32" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX32" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY32" t="inlineStr">
         <is>
-          <t>nervioso</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG32" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI32" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ32" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK32" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL32" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -37843,108 +36667,72 @@
       <c r="ML33" t="n">
         <v>22.3666</v>
       </c>
-      <c r="MM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX33" t="n">
-        <v>0</v>
+      <c r="MM33" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU33" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV33" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MW33" t="inlineStr">
+        <is>
+          <t>metotrexato, ácido fólico, alernix, fluticasona, tacroderm</t>
+        </is>
+      </c>
+      <c r="MX33" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY33" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG33" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH33" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NI33" t="inlineStr">
-        <is>
-          <t>metotrexato, ácido fólico, alernix, fluticasona, tacroderm</t>
-        </is>
-      </c>
-      <c r="NJ33" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK33" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL33" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -38957,108 +37745,72 @@
       <c r="ML34" t="n">
         <v>7.30115</v>
       </c>
-      <c r="MM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX34" t="n">
-        <v>0</v>
+      <c r="MM34" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN34" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU34" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV34" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MW34" t="inlineStr">
+        <is>
+          <t>ansiolíticos</t>
+        </is>
+      </c>
+      <c r="MX34" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY34" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ34" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG34" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH34" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NI34" t="inlineStr">
-        <is>
-          <t>ansiolíticos</t>
-        </is>
-      </c>
-      <c r="NJ34" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK34" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL34" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -40071,108 +38823,72 @@
       <c r="ML35" t="n">
         <v>9.0465</v>
       </c>
-      <c r="MM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX35" t="n">
-        <v>0</v>
+      <c r="MM35" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR35" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU35" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW35" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX35" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY35" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND35" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG35" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI35" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ35" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK35" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL35" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -41185,108 +39901,72 @@
       <c r="ML36" t="n">
         <v>9.155750000000001</v>
       </c>
-      <c r="MM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX36" t="n">
-        <v>0</v>
+      <c r="MM36" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR36" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU36" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV36" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MW36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sólo analgésicos ocasionalmente </t>
+        </is>
+      </c>
+      <c r="MX36" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY36" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND36" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG36" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH36" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NI36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sólo analgésicos ocasionalmente </t>
-        </is>
-      </c>
-      <c r="NJ36" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK36" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL36" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -42299,108 +40979,72 @@
       <c r="ML37" t="n">
         <v>9.2151</v>
       </c>
-      <c r="MM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX37" t="n">
-        <v>0</v>
+      <c r="MM37" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP37" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ37" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR37" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU37" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW37" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX37" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY37" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB37" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC37" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND37" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG37" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI37" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ37" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK37" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL37" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -43413,108 +42057,72 @@
       <c r="ML38" t="n">
         <v>8.882964285714287</v>
       </c>
-      <c r="MM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX38" t="n">
-        <v>0</v>
+      <c r="MM38" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP38" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ38" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR38" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS38" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU38" t="inlineStr">
+        <is>
+          <t>cerveza</t>
+        </is>
+      </c>
+      <c r="MV38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW38" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX38" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY38" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>mas de 8 horas</t>
         </is>
       </c>
       <c r="MZ38" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB38" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC38" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND38" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE38" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF38" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG38" t="inlineStr">
-        <is>
-          <t>cerveza</t>
-        </is>
-      </c>
-      <c r="NH38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI38" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ38" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK38" t="inlineStr">
-        <is>
-          <t>mas de 8 horas</t>
-        </is>
-      </c>
-      <c r="NL38" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -44527,108 +43135,72 @@
       <c r="ML39" t="n">
         <v>8.5595</v>
       </c>
-      <c r="MM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX39" t="n">
-        <v>0</v>
+      <c r="MM39" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN39" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MO39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP39" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MQ39" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MR39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU39" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW39" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX39" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY39" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ39" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NA39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB39" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NC39" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="ND39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG39" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI39" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ39" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK39" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL39" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -45641,108 +44213,72 @@
       <c r="ML40" t="n">
         <v>10.94228571428571</v>
       </c>
-      <c r="MM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX40" t="n">
-        <v>0</v>
+      <c r="MM40" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR40" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS40" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU40" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW40" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX40" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY40" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND40" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE40" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG40" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI40" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ40" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK40" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL40" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -46755,104 +45291,68 @@
       <c r="ML41" t="n">
         <v>8.4717</v>
       </c>
-      <c r="MM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX41" t="n">
-        <v>0</v>
+      <c r="MM41" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR41" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU41" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV41" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MW41" t="inlineStr"/>
+      <c r="MX41" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY41" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND41" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG41" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH41" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NI41" t="inlineStr"/>
-      <c r="NJ41" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK41" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL41" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -47865,108 +46365,72 @@
       <c r="ML42" t="n">
         <v>6.923125</v>
       </c>
-      <c r="MM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX42" t="n">
-        <v>0</v>
+      <c r="MM42" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU42" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW42" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX42" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY42" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG42" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI42" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ42" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK42" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL42" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -48979,108 +47443,72 @@
       <c r="ML43" t="n">
         <v>8.865400000000001</v>
       </c>
-      <c r="MM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX43" t="n">
-        <v>0</v>
+      <c r="MM43" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR43" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU43" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW43" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX43" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY43" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>mas de 8 horas</t>
         </is>
       </c>
       <c r="MZ43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND43" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG43" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI43" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ43" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK43" t="inlineStr">
-        <is>
-          <t>mas de 8 horas</t>
-        </is>
-      </c>
-      <c r="NL43" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -50093,108 +48521,72 @@
       <c r="ML44" t="n">
         <v>6.325875</v>
       </c>
-      <c r="MM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX44" t="n">
-        <v>0</v>
+      <c r="MM44" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR44" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU44" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW44" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX44" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY44" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND44" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG44" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI44" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ44" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK44" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL44" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -51207,108 +49599,72 @@
       <c r="ML45" t="n">
         <v>9.831642857142857</v>
       </c>
-      <c r="MM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX45" t="n">
-        <v>0</v>
+      <c r="MM45" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR45" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS45" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU45" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW45" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX45" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY45" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND45" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE45" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG45" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI45" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ45" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK45" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL45" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -52321,108 +50677,72 @@
       <c r="ML46" t="n">
         <v>6.2485</v>
       </c>
-      <c r="MM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX46" t="n">
-        <v>0</v>
+      <c r="MM46" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR46" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU46" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW46" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX46" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY46" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND46" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG46" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI46" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ46" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK46" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL46" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -53435,108 +51755,72 @@
       <c r="ML47" t="n">
         <v>5.35625</v>
       </c>
-      <c r="MM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX47" t="n">
-        <v>0</v>
+      <c r="MM47" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR47" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MS47" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MT47" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alcohol </t>
+        </is>
+      </c>
+      <c r="MV47" t="inlineStr">
+        <is>
+          <t>diariamente</t>
+        </is>
+      </c>
+      <c r="MW47" t="inlineStr">
+        <is>
+          <t>amlodipina</t>
+        </is>
+      </c>
+      <c r="MX47" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY47" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND47" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NE47" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NF47" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alcohol </t>
-        </is>
-      </c>
-      <c r="NH47" t="inlineStr">
-        <is>
-          <t>diariamente</t>
-        </is>
-      </c>
-      <c r="NI47" t="inlineStr">
-        <is>
-          <t>amlodipina</t>
-        </is>
-      </c>
-      <c r="NJ47" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK47" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL47" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -54549,108 +52833,72 @@
       <c r="ML48" t="n">
         <v>5.7342</v>
       </c>
-      <c r="MM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX48" t="n">
-        <v>0</v>
+      <c r="MM48" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU48" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV48" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MW48" t="inlineStr">
+        <is>
+          <t>ibuprofeno</t>
+        </is>
+      </c>
+      <c r="MX48" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY48" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>3-5 horas</t>
         </is>
       </c>
       <c r="MZ48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG48" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH48" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NI48" t="inlineStr">
-        <is>
-          <t>ibuprofeno</t>
-        </is>
-      </c>
-      <c r="NJ48" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK48" t="inlineStr">
-        <is>
-          <t>3-5 horas</t>
-        </is>
-      </c>
-      <c r="NL48" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
@@ -55663,108 +53911,72 @@
       <c r="ML49" t="n">
         <v>8.2905</v>
       </c>
-      <c r="MM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX49" t="n">
-        <v>0</v>
+      <c r="MM49" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU49" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV49" t="inlineStr">
+        <is>
+          <t>2 o 3 veces a la semana</t>
+        </is>
+      </c>
+      <c r="MW49" t="inlineStr">
+        <is>
+          <t>amlodipina</t>
+        </is>
+      </c>
+      <c r="MX49" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY49" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG49" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH49" t="inlineStr">
-        <is>
-          <t>2 o 3 veces a la semana</t>
-        </is>
-      </c>
-      <c r="NI49" t="inlineStr">
-        <is>
-          <t>amlodipina</t>
-        </is>
-      </c>
-      <c r="NJ49" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK49" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL49" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -56777,108 +54989,72 @@
       <c r="ML50" t="n">
         <v>14.50175</v>
       </c>
-      <c r="MM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX50" t="n">
-        <v>0</v>
+      <c r="MM50" t="inlineStr">
+        <is>
+          <t>aburrido</t>
+        </is>
+      </c>
+      <c r="MN50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MS50" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MT50" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="MU50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cannabis </t>
+        </is>
+      </c>
+      <c r="MV50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW50" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX50" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY50" t="inlineStr">
         <is>
-          <t>aburrido</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NE50" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NF50" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="NG50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cannabis </t>
-        </is>
-      </c>
-      <c r="NH50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI50" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ50" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK50" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL50" t="inlineStr">
         <is>
           <t>6-8 horas</t>
         </is>
@@ -57891,108 +56067,72 @@
       <c r="ML51" t="n">
         <v>4.5581</v>
       </c>
-      <c r="MM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="MX51" t="n">
-        <v>0</v>
+      <c r="MM51" t="inlineStr">
+        <is>
+          <t>atento</t>
+        </is>
+      </c>
+      <c r="MN51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MO51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MP51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MQ51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MR51" t="inlineStr">
+        <is>
+          <t>ocacionalmente</t>
+        </is>
+      </c>
+      <c r="MS51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MT51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="MU51" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MV51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
+      </c>
+      <c r="MW51" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
+      <c r="MX51" t="inlineStr">
+        <is>
+          <t>no consume</t>
+        </is>
       </c>
       <c r="MY51" t="inlineStr">
         <is>
-          <t>atento</t>
+          <t>6-8 horas</t>
         </is>
       </c>
       <c r="MZ51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NA51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NB51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NC51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="ND51" t="inlineStr">
-        <is>
-          <t>ocacionalmente</t>
-        </is>
-      </c>
-      <c r="NE51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NF51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="NG51" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NH51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NI51" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="NJ51" t="inlineStr">
-        <is>
-          <t>no consume</t>
-        </is>
-      </c>
-      <c r="NK51" t="inlineStr">
-        <is>
-          <t>6-8 horas</t>
-        </is>
-      </c>
-      <c r="NL51" t="inlineStr">
         <is>
           <t>3-5 horas</t>
         </is>
